--- a/Statistics/100m Medley_statistics.xlsx
+++ b/Statistics/100m Medley_statistics.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G219"/>
+  <dimension ref="A1:G227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1276,25 +1276,25 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ole Peder Uthus Solum</t>
+          <t>Balder Baarholm</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.04,70</t>
+          <t>1.04,50</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>29.09.2019</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1311,25 +1311,25 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Njål Falch</t>
+          <t>Ole Peder Uthus Solum</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.04,91</t>
+          <t>1.04,70</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>31.10.2009</t>
+          <t>29.09.2019</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1346,20 +1346,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Miguel Marteira do Carvalho</t>
+          <t>Njål Falch</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.04,94</t>
+          <t>1.04,91</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>09.04.2016</t>
+          <t>31.10.2009</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1381,20 +1381,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Magnus Jåtten</t>
+          <t>Miguel Marteira do Carvalho</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1.05,08</t>
+          <t>1.04,94</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>30.03.2025</t>
+          <t>09.04.2016</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1416,12 +1416,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Simen Løvås</t>
+          <t>Magnus Jåtten</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1.05,06</t>
+          <t>1.05,08</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>19.10.2019</t>
+          <t>30.03.2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1451,7 +1451,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ole Peder Uthus Solum</t>
+          <t>Simen Løvås</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>29.09.2018</t>
+          <t>19.10.2019</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1556,12 +1556,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Eirik Hakvåg-Sandengen</t>
+          <t>Tobias Gilbu</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.05,34</t>
+          <t>1.05,31</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>19.01.2020</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1591,12 +1591,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Tobias Gilbu</t>
+          <t>Eirik Hakvåg-Sandengen</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.05,31</t>
+          <t>1.05,34</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>19.01.2020</t>
+          <t>19.01.2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1661,12 +1661,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Balder Baarholm</t>
+          <t>Joakim I. Larsen</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.05,35</t>
+          <t>1.05,36</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>31.10.2009</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1696,20 +1696,20 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Joakim I. Larsen</t>
+          <t>Hans Ourson Liem</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.05,36</t>
+          <t>1.05,43</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>31.10.2009</t>
+          <t>15.01.2023</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1731,25 +1731,25 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Hans Ourson Liem</t>
+          <t>Thomas Trøite</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1.05,43</t>
+          <t>1.05,46</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>15.01.2023</t>
+          <t>28.09.2024</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1766,25 +1766,25 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Thomas Trøite</t>
+          <t>Johannes Tryggestad</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.05,46</t>
+          <t>1.05,53</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>28.09.2024</t>
+          <t>01.10.2022</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1801,20 +1801,20 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Johannes Tryggestad</t>
+          <t>Geir Tvetene Kristiansen</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.05,53</t>
+          <t>1.05,62</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>01.10.2022</t>
+          <t>31.10.2009</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1836,20 +1836,20 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Geir Tvetene Kristiansen</t>
+          <t>Elias Hauge Lien</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.05,62</t>
+          <t>1.05,86</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>31.10.2009</t>
+          <t>08.12.2024</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1871,25 +1871,25 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Elias Hauge Lien</t>
+          <t>Thomas Johansen</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.05,86</t>
+          <t>1.05,94</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>08.12.2024</t>
+          <t>03.10.2015</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1906,25 +1906,25 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Thomas Johansen</t>
+          <t>Christoffer Solberg Jørgensen</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.05,94</t>
+          <t>1.06,07</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>03.10.2015</t>
+          <t>18.06.2016</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1941,20 +1941,20 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Christoffer Solberg Jørgensen</t>
+          <t>Pål Jåtun Pedersen</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.06,07</t>
+          <t>1.06,24</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>18.06.2016</t>
+          <t>04.02.2005</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1976,20 +1976,20 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Pål Jåtun Pedersen</t>
+          <t>Jenny Marandon Natvik</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.06,24</t>
+          <t>1.16,08</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>04.02.2005</t>
+          <t>18.06.2016</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2011,16 +2011,16 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jenny Marandon Natvik</t>
+          <t>Morten Olden Larsen</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.16,08</t>
+          <t>1.06,56</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2046,25 +2046,25 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Morten Olden Larsen</t>
+          <t>Kjersti Arefjord</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.06,56</t>
+          <t>1.16,59</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>18.06.2016</t>
+          <t>10.03.2019</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2081,25 +2081,25 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Kjersti Arefjord</t>
+          <t>Jakob Isaksen</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1.16,59</t>
+          <t>1.06,91</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>10.03.2019</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2116,25 +2116,25 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Jakob Isaksen</t>
+          <t>Vårin Berge Jensås</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1.06,91</t>
+          <t>1.17,40</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>02.03.2019</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Pirbadet</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2151,25 +2151,25 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Vårin Berge Jensås</t>
+          <t>Simon Moe</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1.17,40</t>
+          <t>1.07,85</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>02.03.2019</t>
+          <t>18.06.2016</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Pirbadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2186,25 +2186,25 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Simon Moe</t>
+          <t>Istad Ove-Joakim</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1.07,85</t>
+          <t>1.07,91</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>18.06.2016</t>
+          <t>02.12.2006</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2221,25 +2221,25 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Istad Ove-Joakim</t>
+          <t>Jon Olav Båtbukt</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1.07,91</t>
+          <t>1.07,94</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>02.12.2006</t>
+          <t>07.03.2015</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2256,20 +2256,20 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Jon Olav Båtbukt</t>
+          <t>Einar Woldseth</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1.07,94</t>
+          <t>1.08,04</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>07.03.2015</t>
+          <t>19.01.2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2291,12 +2291,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Einar Woldseth</t>
+          <t>Brage Wetjen Sigernes</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1.08,04</t>
+          <t>1.08,05</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -2304,12 +2304,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>11.02.2023</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2326,12 +2326,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Brage Wetjen Sigernes</t>
+          <t>Jonas Fiskaa Barstad</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1.08,05</t>
+          <t>1.08,06</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>11.02.2023</t>
+          <t>18.06.2016</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2361,20 +2361,20 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Jonas Fiskaa Barstad</t>
+          <t>Kjersti Skauge Bysting</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1.08,06</t>
+          <t>1.18,11</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>18.06.2016</t>
+          <t>18.03.2007</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2396,20 +2396,20 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Kjersti Skauge Bysting</t>
+          <t>Emmelin Munkhaugen</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1.18,11</t>
+          <t>1.18,17</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>18.03.2007</t>
+          <t>26.04.2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2431,12 +2431,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Emmelin Munkhaugen</t>
+          <t>Ådne Viken Refseth</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1.18,17</t>
+          <t>1.08,19</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -2444,12 +2444,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>26.04.2025</t>
+          <t>03.10.2015</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2466,25 +2466,25 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Ådne Viken Refseth</t>
+          <t>Robert Tellefsen</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1.08,19</t>
+          <t>1.08,40</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>03.10.2015</t>
+          <t>20.01.2018</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2501,12 +2501,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Robert Tellefsen</t>
+          <t>Tomas Aarvak</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1.08,40</t>
+          <t>1.08,41</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>20.01.2018</t>
+          <t>26.03.2017</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2536,25 +2536,25 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Tomas Aarvak</t>
+          <t>Margaret Kjøraas</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1.08,41</t>
+          <t>1.18,76</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>26.03.2017</t>
+          <t>04.02.2005</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2571,20 +2571,20 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Margaret Kjøraas</t>
+          <t>Erlend Skogland</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1.18,76</t>
+          <t>1.08,72</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>04.02.2005</t>
+          <t>30.10.2010</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2606,25 +2606,25 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Erlend Skogland</t>
+          <t>Simon Perssønn Mørseth</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1.08,72</t>
+          <t>1.09,08</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>30.10.2010</t>
+          <t>16.02.2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kolvereid</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2676,25 +2676,25 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Simon Perssønn Mørseth</t>
+          <t>Sondre Furmyr Johansen</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1.09,08</t>
+          <t>1.09,34</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>16.02.2025</t>
+          <t>28.01.2024</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2711,25 +2711,25 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sondre Furmyr Johansen</t>
+          <t>Lucas Nachappa Muthanna</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1.09,34</t>
+          <t>1.09,50</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>28.01.2024</t>
+          <t>26.10.2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2886,12 +2886,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Tamer Saleh Abuzid</t>
+          <t>Olav Nygård Bergum</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1.10,06</t>
+          <t>1.10,01</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>20.06.2021</t>
+          <t>26.04.2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2921,12 +2921,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Olav Nygård Bergum</t>
+          <t>Tamer Saleh Abuzid</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1.10,01</t>
+          <t>1.10,06</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>26.04.2025</t>
+          <t>20.06.2021</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3061,25 +3061,25 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Aksel Viken Refseth</t>
+          <t>Ludvig Svendsen</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1.10,27</t>
+          <t>1.10,23</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>01.11.2025</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3096,25 +3096,25 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sander Haugan</t>
+          <t>Aksel Viken Refseth</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1.10,44</t>
+          <t>1.10,27</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>29.09.2019</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3131,25 +3131,25 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Torbjørn Ekrem</t>
+          <t>Sander Haugan</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1.10,50</t>
+          <t>1.10,44</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>30.03.2025</t>
+          <t>29.09.2019</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3166,20 +3166,20 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sander Løvås</t>
+          <t>Torbjørn Ekrem</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1.10,54</t>
+          <t>1.10,50</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>30.03.2025</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3201,20 +3201,20 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Birk Skaalvik Trelstad</t>
+          <t>Sander Løvås</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1.10,81</t>
+          <t>1.10,54</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>02.03.2024</t>
+          <t>19.01.2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3236,20 +3236,20 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Joakim Gjerde</t>
+          <t>Birk Skaalvik Trelstad</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1.10,90</t>
+          <t>1.10,81</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>21.06.2014</t>
+          <t>02.03.2024</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3271,12 +3271,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Bjørnar Bakkejord</t>
+          <t>Joakim Gjerde</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1.10,89</t>
+          <t>1.10,90</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>17.04.2005</t>
+          <t>21.06.2014</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3306,25 +3306,25 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Andreas Aglen Alsos</t>
+          <t>Bjørnar Bakkejord</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1.11,02</t>
+          <t>1.10,89</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>19.06.2022</t>
+          <t>17.04.2005</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3341,25 +3341,25 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Kristin Myhr Pettersen</t>
+          <t>Andreas Aglen Alsos</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1.21,58</t>
+          <t>1.11,02</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>26.10.2013</t>
+          <t>19.06.2022</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3376,25 +3376,25 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sigurd Rodal Leirgulen</t>
+          <t>Kristin Myhr Pettersen</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1.11,35</t>
+          <t>1.21,58</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>25.10.2020</t>
+          <t>26.10.2013</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3411,25 +3411,25 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Reidar Lorentzen</t>
+          <t>Bjørn Eimar Endal Sorteberg</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1.11,82</t>
+          <t>1.11,11</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>02.04.2006</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Lambertseter</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3446,25 +3446,25 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Bjørn Eimar Endal Sorteberg</t>
+          <t>Sigurd Rodal Leirgulen</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1.11,95</t>
+          <t>1.11,35</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>26.04.2025</t>
+          <t>25.10.2020</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3481,20 +3481,20 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Stian Nilsen</t>
+          <t>Reidar Lorentzen</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1.11,92</t>
+          <t>1.11,82</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>17.10.2010</t>
+          <t>02.04.2006</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3516,25 +3516,25 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Hasith Ransiri Attanapola</t>
+          <t>Vishnu Sattanathan</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1.12,19</t>
+          <t>1.11,88</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>20.01.2019</t>
+          <t>01.11.2025</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3551,25 +3551,25 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Jo Kebriel Stølhaug Nor</t>
+          <t>Stian Nilsen</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1.12,18</t>
+          <t>1.11,92</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>02.03.2024</t>
+          <t>17.10.2010</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Lambertseter</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3586,20 +3586,20 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Even Kristoffer Lind Bøckman</t>
+          <t>Hasith Ransiri Attanapola</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1.12,43</t>
+          <t>1.12,19</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>19.01.2020</t>
+          <t>20.01.2019</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3621,25 +3621,25 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Erlend Søderlund</t>
+          <t>Jo Kebriel Stølhaug Nor</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1.12,53</t>
+          <t>1.12,18</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>27.10.2012</t>
+          <t>02.03.2024</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3656,20 +3656,20 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Carl Victor Mukisa Nygård</t>
+          <t>Even Kristoffer Lind Bøckman</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1.12,53</t>
+          <t>1.12,43</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>15.01.2023</t>
+          <t>19.01.2020</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3691,25 +3691,25 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Vishnu Sattanathan</t>
+          <t>Erlend Søderlund</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1.12,69</t>
+          <t>1.12,53</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>27.10.2012</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3726,20 +3726,20 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Ludvig Svendsen</t>
+          <t>Carl Victor Mukisa Nygård</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1.12,75</t>
+          <t>1.12,53</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>26.04.2025</t>
+          <t>15.01.2023</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3796,12 +3796,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Lucas Nachappa Muthanna</t>
+          <t>Håkon Johansen</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1.13,51</t>
+          <t>1.13,52</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -3809,12 +3809,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>24.03.2007</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3831,25 +3831,25 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Håkon Johansen</t>
+          <t>Jostein Ven</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1.13,52</t>
+          <t>1.13,56</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>24.03.2007</t>
+          <t>07.03.2015</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3866,20 +3866,20 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Jostein Ven</t>
+          <t>Ask Yifei Baldersheim</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1.13,56</t>
+          <t>1.13,73</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>07.03.2015</t>
+          <t>02.10.2021</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3901,20 +3901,20 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Ask Yifei Baldersheim</t>
+          <t>Anders Indvik Hageler</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1.13,73</t>
+          <t>1.13,85</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>02.10.2021</t>
+          <t>09.04.2016</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -3936,25 +3936,25 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Anders Indvik Hageler</t>
+          <t>Gunnleif Nielsen</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1.13,85</t>
+          <t>1.13,96</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>09.04.2016</t>
+          <t>04.03.2018</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3971,25 +3971,25 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Gunnleif Nielsen</t>
+          <t>Elian Theodor Kringstad</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1.13,96</t>
+          <t>1.14,13</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>04.03.2018</t>
+          <t>06.04.2024</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4006,25 +4006,25 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Elian Theodor Kringstad</t>
+          <t>Alfred Fenstad Høysæter</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1.14,13</t>
+          <t>1.14,58</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>06.04.2024</t>
+          <t>02.10.2021</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4041,12 +4041,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Alfred Fenstad Høysæter</t>
+          <t>Lev Shestov</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1.14,58</t>
+          <t>1.14,54</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>02.10.2021</t>
+          <t>01.11.2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4076,20 +4076,20 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Tini Fagermo</t>
+          <t>Storm Olander Øvergård</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1.25,58</t>
+          <t>1.14,60</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>09.04.2016</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4111,20 +4111,20 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Ivan Erikovitch Alvestad</t>
+          <t>Tini Fagermo</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1.14,87</t>
+          <t>1.25,58</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>02.10.2021</t>
+          <t>09.04.2016</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4146,20 +4146,20 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Oliver Grøtte Ramstad</t>
+          <t>Pedro Manquehual</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1.15,23</t>
+          <t>1.14,87</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>08.06.2024</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4181,25 +4181,25 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Stian Olsen Sætervik</t>
+          <t>Ivan Erikovitch Alvestad</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1.15,32</t>
+          <t>1.14,87</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>21.10.2007</t>
+          <t>02.10.2021</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Lambertseter</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4216,20 +4216,20 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sondre Grimsmo</t>
+          <t>Oliver Grøtte Ramstad</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1.15,33</t>
+          <t>1.15,23</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>25.01.2008</t>
+          <t>08.06.2024</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -4251,25 +4251,25 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Henning Andersson</t>
+          <t>Stian Olsen Sætervik</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1.15,42</t>
+          <t>1.15,32</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>27.10.2012</t>
+          <t>21.10.2007</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Lambertseter</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4286,20 +4286,20 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Pedro Manquehual</t>
+          <t>Sondre Grimsmo</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1.15,59</t>
+          <t>1.15,33</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>25.01.2008</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4321,20 +4321,20 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Bjarne Forfot</t>
+          <t>Henning Andersson</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1.15,54</t>
+          <t>1.15,42</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>21.10.2017</t>
+          <t>27.10.2012</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4356,25 +4356,25 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Theodor Solheim</t>
+          <t>Bjarne Forfot</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1.15,86</t>
+          <t>1.15,54</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>20.06.2021</t>
+          <t>21.10.2017</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4426,25 +4426,25 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Leif Roar Nordgaard</t>
+          <t>Theodor Solheim</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1.15,90</t>
+          <t>1.15,86</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>13.03.2010</t>
+          <t>20.06.2021</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Stavanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4461,7 +4461,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Lionel Nicolas Weissbrodt</t>
+          <t>Leif Roar Nordgaard</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4474,12 +4474,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>22.10.2023</t>
+          <t>13.03.2010</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4496,25 +4496,25 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Øystein Wethe Hanssen</t>
+          <t>Lionel Nicolas Weissbrodt</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1.16,35</t>
+          <t>1.15,90</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>07.03.2009</t>
+          <t>22.10.2023</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kolvereid</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4531,25 +4531,25 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Bjørn Pedersen</t>
+          <t>Øystein Wethe Hanssen</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1.16,58</t>
+          <t>1.16,35</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>02.10.2010</t>
+          <t>07.03.2009</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4566,25 +4566,25 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Magnus Svindland Næsgaard</t>
+          <t>Bjørn Pedersen</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>1.16,63</t>
+          <t>1.16,58</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>28.01.2024</t>
+          <t>02.10.2010</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4601,20 +4601,20 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Finn Øivind Fevang</t>
+          <t>Magnus Svindland Næsgaard</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>1.16,81</t>
+          <t>1.16,63</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>08.10.2005</t>
+          <t>28.01.2024</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4636,12 +4636,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Mattias Isaksen</t>
+          <t>Finn Øivind Fevang</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>1.16,74</t>
+          <t>1.16,81</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>08.06.2024</t>
+          <t>08.10.2005</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4671,12 +4671,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Tony Christopher Moflag</t>
+          <t>Mattias Isaksen</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>1.16,75</t>
+          <t>1.16,74</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>01.03.2008</t>
+          <t>08.06.2024</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4706,20 +4706,20 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>David Fjeld</t>
+          <t>Tony Christopher Moflag</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>1.17,28</t>
+          <t>1.16,75</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>06.10.2007</t>
+          <t>01.03.2008</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -4776,20 +4776,20 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Storm Olander Øvergård</t>
+          <t>David Fjeld</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1.17,82</t>
+          <t>1.17,28</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>26.04.2025</t>
+          <t>06.10.2007</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -4811,20 +4811,20 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Ellen Kristine Eidsmo Hova</t>
+          <t>Edvin Aurstad Bergum</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1.30,37</t>
+          <t>1.17,94</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>26.04.2025</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -4846,20 +4846,20 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Thomas Stur Ekrem</t>
+          <t>Ellen Kristine Eidsmo Hova</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>1.19,04</t>
+          <t>1.30,37</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>17.06.2023</t>
+          <t>26.04.2025</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -4881,12 +4881,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Daniel Stanislaw Czuba</t>
+          <t>Thomas Stur Ekrem</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1.19,02</t>
+          <t>1.19,04</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>17.06.2023</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -4916,20 +4916,20 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Sondre Aakerholm Adsen</t>
+          <t>Daniel Stanislaw Czuba</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1.19,11</t>
+          <t>1.19,02</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>08.06.2024</t>
+          <t>19.01.2025</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -4951,20 +4951,20 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Edvin Grenne Spangelo</t>
+          <t>Sondre Aakerholm Adsen</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1.19,35</t>
+          <t>1.19,11</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>26.04.2025</t>
+          <t>08.06.2024</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -4986,20 +4986,20 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Leander Gisvold Restad</t>
+          <t>Edvin Grenne Spangelo</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>1.19,65</t>
+          <t>1.19,35</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>19.01.2020</t>
+          <t>26.04.2025</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -5021,16 +5021,16 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Kristian Myhr Høgstøl</t>
+          <t>Leander Gisvold Restad</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1.19,94</t>
+          <t>1.19,65</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -5056,25 +5056,25 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Anton Sergeevich Gorodkov</t>
+          <t>Kristian Myhr Høgstøl</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1.20,03</t>
+          <t>1.19,94</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>24.09.2016</t>
+          <t>19.01.2020</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5091,25 +5091,25 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>David Csejtey</t>
+          <t>Lin Carola Magdalene Nygren</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>1.20,10</t>
+          <t>1.29,36</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>20.06.2021</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5126,20 +5126,20 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Ailin Østerås</t>
+          <t>Anton Sergeevich Gorodkov</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>1.32,00</t>
+          <t>1.20,03</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>01.10.2011</t>
+          <t>24.09.2016</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -5161,25 +5161,25 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Daniel Haugen Ngwenya</t>
+          <t>David Csejtey</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>1.20,37</t>
+          <t>1.20,10</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>19.04.2008</t>
+          <t>20.06.2021</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5196,25 +5196,25 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Eirik Hamnes Ulriksen</t>
+          <t>Ailin Østerås</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>1.20,49</t>
+          <t>1.32,00</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>01.10.2011</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5231,20 +5231,20 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Lin Carola Magdalene Nygren</t>
+          <t>Daniel Haugen Ngwenya</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>1.32,50</t>
+          <t>1.20,37</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>22.02.2025</t>
+          <t>19.04.2008</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -5266,25 +5266,25 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Vegard Maaø</t>
+          <t>Eirik Hamnes Ulriksen</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>1.20,57</t>
+          <t>1.20,49</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>05.12.2009</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5301,25 +5301,25 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Vegard S. Wigum</t>
+          <t>Vegard Maaø</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>1.21,00</t>
+          <t>1.20,57</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>21.06.2014</t>
+          <t>05.12.2009</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5341,15 +5341,15 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>1.21,33</t>
+          <t>1.20,82</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -5371,25 +5371,25 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Kristin Stallvik</t>
+          <t>Vegard S. Wigum</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>1.33,46</t>
+          <t>1.21,00</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>26.03.2017</t>
+          <t>21.06.2014</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5406,25 +5406,25 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Paal Aagaard</t>
+          <t>Edvard Hamnes Ulriksen</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>1.21,78</t>
+          <t>1.21,03</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>13.03.2009</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Kirkenes</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5441,25 +5441,25 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Conrad Sippala Hassel</t>
+          <t>Sigurd Øie Seland</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>1.22,37</t>
+          <t>1.21,37</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>19.01.2020</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5476,25 +5476,25 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Ingjerd Jepsen Vegge</t>
+          <t>Kristin Stallvik</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>1.34,37</t>
+          <t>1.33,46</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>12.11.2011</t>
+          <t>26.03.2017</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5511,25 +5511,25 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Eilert Juul Wolfgang</t>
+          <t>Liv Løfaldli</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>1.22,75</t>
+          <t>1.31,41</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>26.10.2013</t>
+          <t>01.11.2025</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5546,25 +5546,25 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Christian Dahle-Øfsti</t>
+          <t>Paal Aagaard</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>1.22,98</t>
+          <t>1.21,78</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>02.06.2013</t>
+          <t>13.03.2009</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Stavanger</t>
+          <t>Kirkenes</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5581,25 +5581,25 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Brage Gylseth Dahl</t>
+          <t>Ingjerd Jepsen Vegge</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>1.23,11</t>
+          <t>1.34,37</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>12.11.2011</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5616,20 +5616,20 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Njål Høie</t>
+          <t>Conrad Sippala Hassel</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>1.23,33</t>
+          <t>1.22,37</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>20.06.2015</t>
+          <t>19.01.2020</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5651,25 +5651,25 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Oscar Kvaløy Tiller</t>
+          <t>Eilert Juul Wolfgang</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>1.23,65</t>
+          <t>1.22,75</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>20.06.2021</t>
+          <t>26.10.2013</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5686,25 +5686,25 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Liv Løfaldli</t>
+          <t>Christian Dahle-Øfsti</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>1.36,36</t>
+          <t>1.22,98</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>16.02.2025</t>
+          <t>02.06.2013</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5721,25 +5721,25 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Isabel Ødegård Pedersen</t>
+          <t>Fredrik Holberg</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>1.36,57</t>
+          <t>1.23,01</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5756,20 +5756,20 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Fredrik Holberg</t>
+          <t>Brage Gylseth Dahl</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>1.26,71</t>
+          <t>1.23,11</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>183</v>
+        <v>208</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -5791,20 +5791,20 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Edvard Hamnes Ulriksen</t>
+          <t>Njål Høie</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>1.27,09</t>
+          <t>1.23,33</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>08.12.2024</t>
+          <t>20.06.2015</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -5826,20 +5826,20 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Vår Kristine Sollien Skar</t>
+          <t>Oscar Kvaløy Tiller</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>1.39,74</t>
+          <t>1.23,65</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>05.03.2016</t>
+          <t>20.06.2021</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -5861,25 +5861,25 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Gunhild Furuholt Valle</t>
+          <t>Olav Høyland Hofstad</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>1.39,91</t>
+          <t>1.24,22</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>26.04.2025</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5896,25 +5896,25 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Jonas D. Lesund</t>
+          <t>Isabel Ødegård Pedersen</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>1.27,68</t>
+          <t>1.36,57</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>10.11.2012</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5931,20 +5931,20 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Eirik Ingeberg Garshol</t>
+          <t>Gunhild Furuholt Valle</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>1.28,76</t>
+          <t>1.34,53</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>08.12.2024</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -5966,20 +5966,20 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Ingeborg Strandenes</t>
+          <t>Vår Kristine Sollien Skar</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>1.42,81</t>
+          <t>1.39,74</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>26.04.2025</t>
+          <t>05.03.2016</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -6001,25 +6001,25 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Edvin Aurstad Bergum</t>
+          <t>Jonas D. Lesund</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>1.30,05</t>
+          <t>1.27,68</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>02.03.2024</t>
+          <t>10.11.2012</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6036,20 +6036,20 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Even Greiff</t>
+          <t>Eirik Ingeberg Garshol</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>1.30,35</t>
+          <t>1.28,76</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>28.01.2024</t>
+          <t>08.12.2024</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -6071,25 +6071,25 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Bjørn Marius Hegge</t>
+          <t>Ingeborg Strandenes</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>1.30,53</t>
+          <t>1.39,53</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>10.03.2019</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6106,20 +6106,20 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>William Wale</t>
+          <t>Even Greiff</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>1.30,88</t>
+          <t>1.30,35</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>21.06.2014</t>
+          <t>28.01.2024</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -6141,25 +6141,25 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Jakob M. Tjøstheim</t>
+          <t>Bjørn Marius Hegge</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>1.31,77</t>
+          <t>1.30,53</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>21.06.2014</t>
+          <t>10.03.2019</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6176,25 +6176,25 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Maiken Belsvik</t>
+          <t>William Wale</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>1.46,25</t>
+          <t>1.30,88</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>12.03.2005</t>
+          <t>21.06.2014</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6211,25 +6211,25 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Kolbjørn Renhult Skaug</t>
+          <t>Jakob M. Tjøstheim</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>1.32,91</t>
+          <t>1.31,77</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>25.10.2014</t>
+          <t>21.06.2014</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6246,25 +6246,25 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Thomas Paulsen</t>
+          <t>Maiken Belsvik</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>1.32,87</t>
+          <t>1.46,25</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>01.03.2014</t>
+          <t>12.03.2005</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6281,20 +6281,20 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Setareh Kulsum Sigrid Feyzi</t>
+          <t>Cornelius Wik</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>1.46,92</t>
+          <t>1.32,93</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>10.03.2018</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -6316,25 +6316,25 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Robin von Bargen</t>
+          <t>Kolbjørn Renhult Skaug</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>1.33,37</t>
+          <t>1.32,91</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>30.10.2010</t>
+          <t>25.10.2014</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6351,25 +6351,25 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Magnus Bakkejord</t>
+          <t>Thomas Paulsen</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>1.33,47</t>
+          <t>1.32,87</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>12.11.2011</t>
+          <t>01.03.2014</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6386,25 +6386,25 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Peder Lund Juul</t>
+          <t>Setareh Kulsum Sigrid Feyzi</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>1.33,80</t>
+          <t>1.46,92</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>02.11.2024</t>
+          <t>10.03.2018</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6421,20 +6421,20 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Sondre Thorgaard</t>
+          <t>Robin von Bargen</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>1.34,01</t>
+          <t>1.33,37</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>02.10.2021</t>
+          <t>30.10.2010</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -6456,25 +6456,25 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Marcus Thalberg Fagerheim</t>
+          <t>Magnus Bakkejord</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>1.34,06</t>
+          <t>1.33,47</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>01.10.2011</t>
+          <t>12.11.2011</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6491,25 +6491,25 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Jon Noé Høye</t>
+          <t>Peder Lund Juul</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>1.35,30</t>
+          <t>1.33,80</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>21.10.2018</t>
+          <t>02.11.2024</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6526,25 +6526,25 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Marit Søberg</t>
+          <t>Sondre Thorgaard</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>1.49,52</t>
+          <t>1.34,01</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>03.10.2009</t>
+          <t>02.10.2021</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6561,25 +6561,25 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Tymofii Dzisiak</t>
+          <t>Marcus Thalberg Fagerheim</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>1.35,80</t>
+          <t>1.34,06</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>22.02.2025</t>
+          <t>01.10.2011</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6596,25 +6596,25 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Anton Hoel</t>
+          <t>Bernard Smuk</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>1.36,50</t>
+          <t>1.34,40</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>10.11.2012</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6631,25 +6631,25 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Kasper Steen Jensen</t>
+          <t>Jon Noé Høye</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>1.36,32</t>
+          <t>1.35,30</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>21.10.2018</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6666,25 +6666,25 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Ingolf Nicholay Stenskrog</t>
+          <t>Marit Søberg</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>1.36,75</t>
+          <t>1.49,52</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>02.11.2013</t>
+          <t>03.10.2009</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6701,25 +6701,25 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Jesper Julius Sundseth Skjærli</t>
+          <t>Tymofii Dzisiak</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>1.37,02</t>
+          <t>1.35,80</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>22.02.2025</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6736,16 +6736,16 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Filip Dalsaune</t>
+          <t>Kasper Steen Jensen</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>1.36,99</t>
+          <t>1.36,32</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -6771,25 +6771,25 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Cornelius Wik</t>
+          <t>Anton Hoel</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>1.37,76</t>
+          <t>1.36,50</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>08.06.2024</t>
+          <t>10.11.2012</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6806,20 +6806,20 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Arild Håkonsen Stixrud</t>
+          <t>Ingolf Nicholay Stenskrog</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>1.38,88</t>
+          <t>1.36,75</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>08.06.2024</t>
+          <t>02.11.2013</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -6841,20 +6841,20 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Rasmus Larsen Natvig</t>
+          <t>Filip Dalsaune</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>1.39,55</t>
+          <t>1.36,99</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -6876,20 +6876,20 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Lukas Katekawa Theting</t>
+          <t>Jesper Julius Sundseth Skjærli</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>1.40,58</t>
+          <t>1.37,02</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>07.03.2020</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -6911,25 +6911,25 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Magnus Hestvik Larsen</t>
+          <t>Erik Solbakken Andersen</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>1.41,79</t>
+          <t>1.37,49</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>19.04.2009</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6946,20 +6946,20 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Christopher Janjua</t>
+          <t>Ingeborg Vold Kirkvold</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>1.42,83</t>
+          <t>1.49,35</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>03.04.2005</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -6981,25 +6981,25 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Randi Leiknes</t>
+          <t>Arild Håkonsen Stixrud</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>1.57,85</t>
+          <t>1.38,88</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>23.02.2008</t>
+          <t>08.06.2024</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7016,20 +7016,20 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Sigurd Øie Seland</t>
+          <t>Rasmus Larsen Natvig</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>1.42,68</t>
+          <t>1.39,55</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>28.01.2024</t>
+          <t>19.01.2025</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -7051,20 +7051,20 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Johan Mostervik</t>
+          <t>Marius Gaup</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>1.43,66</t>
+          <t>1.40,11</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>20.06.2015</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -7086,25 +7086,25 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Ingvar Høgås Wik</t>
+          <t>Lukas Katekawa Theting</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>1.45,00</t>
+          <t>1.40,58</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>08.11.2014</t>
+          <t>07.03.2020</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -7121,20 +7121,20 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Sigurd Kristoffersen Torvik</t>
+          <t>Lilly Fludal Osland</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>1.48,29</t>
+          <t>1.52,56</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -7156,25 +7156,25 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Brage Kaminka Heiberg</t>
+          <t>Magnus Hestvik Larsen</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>1.48,65</t>
+          <t>1.41,79</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>15.04.2023</t>
+          <t>19.04.2009</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -7191,20 +7191,20 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Bernard Smuk</t>
+          <t>Christopher Janjua</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>1.48,78</t>
+          <t>1.42,83</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>19.03.2023</t>
+          <t>03.04.2005</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -7226,25 +7226,25 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Eirik Borgen</t>
+          <t>Randi Leiknes</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>1.49,53</t>
+          <t>1.57,85</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>10.03.2012</t>
+          <t>23.02.2008</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -7261,25 +7261,25 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Jørgen Norvik Skeide</t>
+          <t>Johan Mostervik</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>1.49,48</t>
+          <t>1.43,66</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>29.10.2005</t>
+          <t>20.06.2015</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -7296,25 +7296,25 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Einar Risholt Moen</t>
+          <t>Mikkel Fenstad</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>1.49,65</t>
+          <t>1.44,38</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>02.03.2013</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -7331,25 +7331,25 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Fredrik Hårsaker Myrenget</t>
+          <t>Ingvar Høgås Wik</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>1.52,91</t>
+          <t>1.45,00</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>20.01.2018</t>
+          <t>08.11.2014</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -7366,25 +7366,25 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Alexander Vik Tastad</t>
+          <t>Ragnhild Fjermestad</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>1.52,83</t>
+          <t>1.57,42</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>01.04.2006</t>
+          <t>01.11.2025</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -7401,20 +7401,20 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Jesper Øvermo Johansen</t>
+          <t>Sigurd Kristoffersen Torvik</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>1.52,75</t>
+          <t>1.48,29</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>07.03.2020</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -7436,25 +7436,25 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Nataniel Skjøndal-Bar</t>
+          <t>Brage Kaminka Heiberg</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>1.53,51</t>
+          <t>1.48,65</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>07.03.2020</t>
+          <t>15.04.2023</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -7471,25 +7471,25 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Hans Otto Søyseth</t>
+          <t>Eirik Borgen</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>1.54,28</t>
+          <t>1.49,53</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>07.03.2015</t>
+          <t>10.03.2012</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -7506,25 +7506,25 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Vegard Olsvold</t>
+          <t>Jørgen Norvik Skeide</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>1.53,90</t>
+          <t>1.49,48</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>19.01.2020</t>
+          <t>29.10.2005</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -7541,20 +7541,20 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>William Johannes Kirkelund Kristiansen</t>
+          <t>Einar Risholt Moen</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>1.54,57</t>
+          <t>1.49,65</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>14.11.2021</t>
+          <t>02.03.2013</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -7576,20 +7576,20 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Emil Gustafson</t>
+          <t>Jesper Øvermo Johansen</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>1.57,75</t>
+          <t>1.52,75</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>02.03.2013</t>
+          <t>07.03.2020</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -7611,20 +7611,20 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Guangzhi Ma</t>
+          <t>Fredrik Hårsaker Myrenget</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>1.59,27</t>
+          <t>1.52,91</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>19.03.2006</t>
+          <t>20.01.2018</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -7646,25 +7646,25 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Mikkel Fenstad</t>
+          <t>Alexander Vik Tastad</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2.01,26</t>
+          <t>1.52,83</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>02.03.2024</t>
+          <t>01.04.2006</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -7681,25 +7681,25 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Eirik Solligård</t>
+          <t>Nataniel Skjøndal-Bar</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2.01,90</t>
+          <t>1.53,51</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>19.04.2009</t>
+          <t>07.03.2020</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -7716,20 +7716,20 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Daniel Karlsen</t>
+          <t>Vegard Olsvold</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2.02,10</t>
+          <t>1.53,90</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>21.06.2014</t>
+          <t>19.01.2020</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -7751,20 +7751,20 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Gajithsing Ajeethsing</t>
+          <t>Hans Otto Søyseth</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2.02,21</t>
+          <t>1.54,28</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>02.10.2021</t>
+          <t>07.03.2015</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -7786,20 +7786,20 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Erik Solbakken Andersen</t>
+          <t>William Johannes Kirkelund Kristiansen</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2.02,75</t>
+          <t>1.54,57</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>02.03.2024</t>
+          <t>14.11.2021</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -7821,20 +7821,20 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Nikan Ommani</t>
+          <t>Emil Gustafson</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2.02,99</t>
+          <t>1.57,75</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>08.06.2024</t>
+          <t>02.03.2013</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -7856,20 +7856,20 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Jo Svendsen</t>
+          <t>Guangzhi Ma</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2.03,34</t>
+          <t>1.59,27</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>07.03.2020</t>
+          <t>19.03.2006</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -7891,25 +7891,25 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Markus Indergård Holm</t>
+          <t>Barnaby Lee_Wright</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2.04,49</t>
+          <t>2.00,77</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>19.04.2008</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -7926,25 +7926,25 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Morten Johansen</t>
+          <t>Eirik Solligård</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2.09,11</t>
+          <t>2.01,90</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>03.04.2005</t>
+          <t>19.04.2009</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -7961,20 +7961,20 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Arvid Hageler</t>
+          <t>Gajithsing Ajeethsing</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2.17,60</t>
+          <t>2.02,21</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>30.03.2025</t>
+          <t>02.10.2021</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -7996,20 +7996,20 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Lars Berg Lerstad</t>
+          <t>Daniel Karlsen</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2.19,50</t>
+          <t>2.02,10</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>02.03.2013</t>
+          <t>21.06.2014</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -8031,20 +8031,20 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Theodor Hoff</t>
+          <t>Nikan Ommani</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2.19,62</t>
+          <t>2.02,99</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>02.03.2013</t>
+          <t>08.06.2024</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -8066,33 +8066,313 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
+          <t>Jo Svendsen</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2.03,34</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>63</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>07.03.2020</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Markus Indergård Holm</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2.04,49</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>62</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>19.04.2008</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Stjørdal</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Guy Løfaldli</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2.04,32</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>62</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>27.09.2025</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Morten Johansen</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2.09,11</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>55</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>03.04.2005</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Noah Kvam Haaheim</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2.13,45</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>50</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>27.09.2025</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Arvid Hageler</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2.17,60</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>45</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>30.03.2025</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Lars Berg Lerstad</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2.19,50</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>44</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>02.03.2013</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Theodor Hoff</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2.19,62</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>43</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>02.03.2013</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
           <t>Mattis Holt</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
+      <c r="B227" t="inlineStr">
         <is>
           <t>2.54,42</t>
         </is>
       </c>
-      <c r="C219" t="n">
+      <c r="C227" t="n">
         <v>22</v>
       </c>
-      <c r="D219" t="inlineStr">
+      <c r="D227" t="inlineStr">
         <is>
           <t>03.04.2005</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>Trondheim</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>25m</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr">
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -8160,7 +8440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G199"/>
+  <dimension ref="A1:G201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8208,20 +8488,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.03,84</t>
+          <t>1.02,21</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>17.11.2024</t>
+          <t>16.11.2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bodø</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -9183,12 +9463,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Christiana Bjørkli</t>
+          <t>Sissel Furuholt Valle</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1.13,32</t>
+          <t>1.11,51</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -9196,12 +9476,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>21.10.2007</t>
+          <t>26.10.2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lambertseter</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -9218,25 +9498,25 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Signe Hogstad</t>
+          <t>Christiana Bjørkli</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.13,94</t>
+          <t>1.13,32</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>30.03.2025</t>
+          <t>21.10.2007</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Lambertseter</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -9288,20 +9568,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Maja Graczyk</t>
+          <t>Signe Hogstad</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.14,17</t>
+          <t>1.13,94</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>20.01.2019</t>
+          <t>30.03.2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -9323,25 +9603,25 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Aurora Moen Wannebo</t>
+          <t>Maja Graczyk</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.14,48</t>
+          <t>1.14,17</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>25.10.2014</t>
+          <t>20.01.2019</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -9358,25 +9638,25 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malin Schanke Tømmervik</t>
+          <t>Aurora Moen Wannebo</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1.14,56</t>
+          <t>1.14,48</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>05.12.2009</t>
+          <t>25.10.2014</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -9393,12 +9673,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sissel Furuholt Valle</t>
+          <t>Malin Schanke Tømmervik</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.14,58</t>
+          <t>1.14,56</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -9406,12 +9686,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>05.12.2009</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -9743,12 +10023,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Annika Krill</t>
+          <t>Carina Aadahl</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1.16,85</t>
+          <t>1.16,84</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -9756,12 +10036,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>04.02.2005</t>
+          <t>24.09.2016</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9778,12 +10058,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Carina Aadahl</t>
+          <t>Annika Krill</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.16,84</t>
+          <t>1.16,85</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -9791,12 +10071,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>24.09.2016</t>
+          <t>04.02.2005</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9988,25 +10268,25 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Heidi Elisabeth Ysland</t>
+          <t>Alexandra Contreras Jimenez</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1.18,01</t>
+          <t>1.15,79</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>24.09.2016</t>
+          <t>26.10.2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10023,25 +10303,25 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Miriam Vedvik</t>
+          <t>Heidi Elisabeth Ysland</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1.18,20</t>
+          <t>1.18,01</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>19.10.2008</t>
+          <t>24.09.2016</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Lambertseter</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10058,25 +10338,25 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Lisa Ling Klauseth Liasjø</t>
+          <t>Miriam Vedvik</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1.18,25</t>
+          <t>1.18,20</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>29.02.2020</t>
+          <t>19.10.2008</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Lambertseter</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10128,20 +10408,20 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Camilla Dahle-Øfsti</t>
+          <t>Lisa Ling Klauseth Liasjø</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1.18,41</t>
+          <t>1.18,25</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>26.09.2015</t>
+          <t>29.02.2020</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -10163,12 +10443,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Olea Winnberg</t>
+          <t>Nora Yian Baldersheim</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1.18,42</t>
+          <t>1.18,41</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -10176,12 +10456,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>19.10.2024</t>
+          <t>24.10.2021</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -10198,12 +10478,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Nora Yian Baldersheim</t>
+          <t>Olea Winnberg</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1.18,41</t>
+          <t>1.18,42</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -10211,12 +10491,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>24.10.2021</t>
+          <t>19.10.2024</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -10233,25 +10513,25 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Thea Haugan</t>
+          <t>Camilla Dahle-Øfsti</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1.18,45</t>
+          <t>1.18,41</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>07.03.2020</t>
+          <t>26.09.2015</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -10268,12 +10548,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Mari Helen Hammer</t>
+          <t>Thea Haugan</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1.18,50</t>
+          <t>1.18,45</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -10281,7 +10561,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>07.10.2006</t>
+          <t>07.03.2020</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -10303,20 +10583,20 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cesilie Solberg Jørgensen</t>
+          <t>Mari Helen Hammer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1.18,63</t>
+          <t>1.18,50</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>07.03.2015</t>
+          <t>07.10.2006</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -10338,25 +10618,25 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Edle Lund</t>
+          <t>Cesilie Solberg Jørgensen</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1.18,68</t>
+          <t>1.18,63</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>22.10.2016</t>
+          <t>07.03.2015</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -10373,25 +10653,25 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cecilie Arentz</t>
+          <t>Edle Lund</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1.18,77</t>
+          <t>1.18,68</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>10.03.2012</t>
+          <t>22.10.2016</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -10408,12 +10688,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Live Killingberg Sandberg</t>
+          <t>Cecilie Arentz</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1.18,72</t>
+          <t>1.18,77</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -10421,12 +10701,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>29.02.2020</t>
+          <t>10.03.2012</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -10443,25 +10723,25 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Marie Skuseth</t>
+          <t>Live Killingberg Sandberg</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1.18,85</t>
+          <t>1.18,72</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>29.10.2023</t>
+          <t>29.02.2020</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stavanger</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -10478,25 +10758,25 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Monica Wold Gustafson</t>
+          <t>Marie Skuseth</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1.18,99</t>
+          <t>1.18,85</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>09.04.2016</t>
+          <t>29.10.2023</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -10513,25 +10793,25 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Oda Sem Austmo</t>
+          <t>Monica Wold Gustafson</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1.19,07</t>
+          <t>1.18,99</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>28.09.2013</t>
+          <t>09.04.2016</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -10548,25 +10828,25 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sylvia Yang</t>
+          <t>Oda Sem Austmo</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1.19,11</t>
+          <t>1.19,07</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>26.01.2007</t>
+          <t>28.09.2013</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -10583,12 +10863,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Marthe Kalvik</t>
+          <t>Torborg Duesten Blokkum</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1.19,12</t>
+          <t>1.19,11</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -10596,12 +10876,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>16.09.2007</t>
+          <t>02.04.2011</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -10618,7 +10898,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Torborg Duesten Blokkum</t>
+          <t>Sylvia Yang</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -10631,12 +10911,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>02.04.2011</t>
+          <t>26.01.2007</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -10653,12 +10933,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Nora Kristine Rasmussen</t>
+          <t>Marthe Kalvik</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1.19,09</t>
+          <t>1.19,12</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -10666,7 +10946,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>20.06.2015</t>
+          <t>16.09.2007</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -10688,20 +10968,20 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Thora Bjarnøe Brandsegg</t>
+          <t>Nora Kristine Rasmussen</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1.19,30</t>
+          <t>1.19,09</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>04.03.2023</t>
+          <t>20.06.2015</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -10723,20 +11003,20 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Aase Bjørnsdatter Paulsen</t>
+          <t>Thora Bjarnøe Brandsegg</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1.19,40</t>
+          <t>1.19,30</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>20.01.2018</t>
+          <t>04.03.2023</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -10758,12 +11038,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Dorottya Csejtey</t>
+          <t>Aase Bjørnsdatter Paulsen</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1.19,41</t>
+          <t>1.19,40</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -10771,7 +11051,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>19.01.2020</t>
+          <t>20.01.2018</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -10793,20 +11073,20 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Emilie Ying Ulstad Hovland</t>
+          <t>Dorottya Csejtey</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1.19,57</t>
+          <t>1.19,41</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>30.03.2025</t>
+          <t>19.01.2020</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -10828,20 +11108,20 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Ane Viken Refseth</t>
+          <t>Emilie Ying Ulstad Hovland</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1.20,06</t>
+          <t>1.19,57</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>20.06.2015</t>
+          <t>30.03.2025</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -10863,20 +11143,20 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Emma Lu Tjeldvoll</t>
+          <t>Ane Viken Refseth</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1.20,15</t>
+          <t>1.20,06</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>15.01.2023</t>
+          <t>20.06.2015</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -10898,25 +11178,25 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Guro Rønningen Osmoen</t>
+          <t>Emma Lu Tjeldvoll</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1.20,22</t>
+          <t>1.20,15</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>16.02.2025</t>
+          <t>15.01.2023</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -10933,25 +11213,25 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Hedda Fosseng Traa</t>
+          <t>Guro Rønningen Osmoen</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1.20,65</t>
+          <t>1.20,22</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>04.03.2017</t>
+          <t>16.02.2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kolvereid</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -10968,20 +11248,20 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Solveig Natvig Løvseth</t>
+          <t>Hedda Fosseng Traa</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1.20,66</t>
+          <t>1.20,65</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>20.06.2015</t>
+          <t>04.03.2017</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -11003,20 +11283,20 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Anita Klungervik</t>
+          <t>Solveig Natvig Løvseth</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1.20,85</t>
+          <t>1.20,66</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>28.01.2024</t>
+          <t>20.06.2015</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -11038,12 +11318,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Alexandra Contreras Jimenez</t>
+          <t>Anita Klungervik</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1.20,86</t>
+          <t>1.20,85</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -11051,7 +11331,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>26.04.2025</t>
+          <t>28.01.2024</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -11388,25 +11668,25 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Hedda Østgaard</t>
+          <t>Emre Vold Kirkvold</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1.22,24</t>
+          <t>1.11,47</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>14.11.2009</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -11458,25 +11738,25 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Elise Nygård</t>
+          <t>Hedda Østgaard</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1.22,34</t>
+          <t>1.22,24</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>02.04.2011</t>
+          <t>14.11.2009</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -11493,25 +11773,25 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Anna Svendsen</t>
+          <t>Elise Nygård</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1.22,61</t>
+          <t>1.22,34</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>07.03.2020</t>
+          <t>02.04.2011</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -11528,25 +11808,25 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Aurora Alexandra Bjordal</t>
+          <t>Anna Svendsen</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1.22,64</t>
+          <t>1.22,61</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>12.02.2022</t>
+          <t>07.03.2020</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -11563,25 +11843,25 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Hanne Søyseth</t>
+          <t>Aurora Alexandra Bjordal</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1.23,04</t>
+          <t>1.22,64</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>18.06.2016</t>
+          <t>12.02.2022</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -11598,20 +11878,20 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Emre Vold Kirkvold</t>
+          <t>Hanne Søyseth</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1.12,43</t>
+          <t>1.23,04</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>18.06.2016</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -11668,25 +11948,25 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Hansine Rindberg Monsø</t>
+          <t>Nicole Kulagina</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1.23,20</t>
+          <t>1.21,02</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>26.04.2025</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -11703,25 +11983,25 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Anette Haugsbakk Fløan</t>
+          <t>Hansine Rindberg Monsø</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1.23,36</t>
+          <t>1.23,20</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>24.03.2007</t>
+          <t>26.04.2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -11738,25 +12018,25 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Linn Amalie Aresvik</t>
+          <t>Anette Haugsbakk Fløan</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1.23,63</t>
+          <t>1.23,36</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>10.11.2012</t>
+          <t>24.03.2007</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -11773,25 +12053,25 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Erika Nicole Hagen</t>
+          <t>Linn Amalie Aresvik</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1.23,79</t>
+          <t>1.23,63</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>12.02.2022</t>
+          <t>10.11.2012</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -11843,25 +12123,25 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Alisa Kulagina</t>
+          <t>Erika Nicole Hagen</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1.24,00</t>
+          <t>1.23,79</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>26.04.2025</t>
+          <t>12.02.2022</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -11878,25 +12158,25 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Frode Elverum</t>
+          <t>Alisa Kulagina</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1.13,31</t>
+          <t>1.24,00</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>08.03.2013</t>
+          <t>26.04.2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Stord</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -11913,25 +12193,25 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Othelie Annette Høie</t>
+          <t>Frode Elverum</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1.24,19</t>
+          <t>1.13,31</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>20.06.2015</t>
+          <t>08.03.2013</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stord</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -11948,25 +12228,25 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Marthe Eline Waagø-Hansen</t>
+          <t>Othelie Annette Høie</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1.24,48</t>
+          <t>1.24,19</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>24.03.2007</t>
+          <t>20.06.2015</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -11983,25 +12263,25 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Elisabeth Holm</t>
+          <t>Marthe Eline Waagø-Hansen</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1.25,00</t>
+          <t>1.24,48</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>12.03.2005</t>
+          <t>24.03.2007</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -12018,25 +12298,25 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Kyrre Moljord</t>
+          <t>Elisabeth Holm</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1.14,51</t>
+          <t>1.25,00</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>04.02.2005</t>
+          <t>12.03.2005</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -12053,20 +12333,20 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Sofie Hepsø</t>
+          <t>Kyrre Moljord</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1.25,62</t>
+          <t>1.14,51</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>04.02.2005</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -12088,20 +12368,20 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Hedda Grimstad-Johannessen</t>
+          <t>Sofie Hepsø</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1.26,11</t>
+          <t>1.25,62</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>02.10.2021</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -12123,25 +12403,25 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Radana Konarikova</t>
+          <t>Helle Johnsen Selsås</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1.26,32</t>
+          <t>1.23,86</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>18.03.2007</t>
+          <t>01.11.2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Kristiansand</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -12158,20 +12438,20 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Kristina Aleman Sandsund</t>
+          <t>Hedda Grimstad-Johannessen</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1.26,47</t>
+          <t>1.26,11</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>02.10.2021</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -12193,25 +12473,25 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Oline Skjønberg</t>
+          <t>Radana Konarikova</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1.26,89</t>
+          <t>1.26,32</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>30.11.2019</t>
+          <t>18.03.2007</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Kristiansand</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -12228,25 +12508,25 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Frida Pauline Busch</t>
+          <t>Kristina Aleman Sandsund</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1.26,85</t>
+          <t>1.26,47</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>24.10.2021</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -12263,25 +12543,25 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Nicole Kulagina</t>
+          <t>Michaela Josefin Abeleva Barrera</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1.26,98</t>
+          <t>1.24,38</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>26.04.2025</t>
+          <t>01.11.2025</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -12298,25 +12578,25 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Juliane-Linnea Tybell Svenum</t>
+          <t>Oline Skjønberg</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>1.27,07</t>
+          <t>1.26,89</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>20.06.2021</t>
+          <t>30.11.2019</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -12333,25 +12613,25 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Sigrid Eldholm</t>
+          <t>Frida Pauline Busch</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>1.27,51</t>
+          <t>1.26,85</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>02.03.2019</t>
+          <t>24.10.2021</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Pirbadet</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -12368,25 +12648,25 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Ola vatn Gundersen</t>
+          <t>Juliane-Linnea Tybell Svenum</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>1.16,37</t>
+          <t>1.27,07</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>29.09.2019</t>
+          <t>20.06.2021</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -12403,25 +12683,25 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Silje Dahle</t>
+          <t>Sigrid Eldholm</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>1.27,78</t>
+          <t>1.27,51</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>03.03.2018</t>
+          <t>02.03.2019</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Pirbadet</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -12438,25 +12718,25 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Hilde Stene Rygh</t>
+          <t>Ola vatn Gundersen</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>1.27,80</t>
+          <t>1.16,37</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>02.04.2011</t>
+          <t>29.09.2019</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -12473,25 +12753,25 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Line Steine Bertelsen</t>
+          <t>Silje Dahle</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>1.27,91</t>
+          <t>1.27,78</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>02.10.2021</t>
+          <t>03.03.2018</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -12508,25 +12788,25 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Julie Wiik Arnesen</t>
+          <t>Hilde Stene Rygh</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1.28,04</t>
+          <t>1.27,80</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>30.11.2019</t>
+          <t>02.04.2011</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -12543,20 +12823,20 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Sofia Bjørklund Mora</t>
+          <t>Line Steine Bertelsen</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1.28,04</t>
+          <t>1.27,91</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>20.06.2015</t>
+          <t>02.10.2021</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -12578,25 +12858,25 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Helle Johnsen Selsås</t>
+          <t>Julie Wiik Arnesen</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>1.28,49</t>
+          <t>1.28,04</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>08.12.2024</t>
+          <t>30.11.2019</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -12613,20 +12893,20 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Sara Skaalvik Trelstad</t>
+          <t>Sofia Bjørklund Mora</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1.28,59</t>
+          <t>1.28,04</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>01.03.2014</t>
+          <t>20.06.2015</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -12648,25 +12928,25 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Sunniva Belsnes</t>
+          <t>Sara Skaalvik Trelstad</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1.29,01</t>
+          <t>1.28,59</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>08.10.2016</t>
+          <t>01.03.2014</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -12683,25 +12963,25 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Michaela Josefin Abeleva Barrera</t>
+          <t>Sunniva Belsnes</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1.29,24</t>
+          <t>1.29,01</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>08.10.2016</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -12718,12 +12998,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Sofie Hoff</t>
+          <t>Elsa Dragsten Wake</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>1.30,19</t>
+          <t>1.28,04</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -12731,12 +13011,12 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>06.04.2024</t>
+          <t>01.11.2025</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -12753,25 +13033,25 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Helene Marie Haram</t>
+          <t>Sofie Hoff</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1.30,86</t>
+          <t>1.30,19</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>27.10.2019</t>
+          <t>06.04.2024</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -12788,25 +13068,25 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Pia Helena Wildhagen</t>
+          <t>Helene Marie Haram</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1.31,30</t>
+          <t>1.30,86</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>10.03.2018</t>
+          <t>27.10.2019</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -12823,20 +13103,20 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Ina Birgitte Eidsmo Hova</t>
+          <t>Pia Helena Wildhagen</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>1.31,48</t>
+          <t>1.31,30</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>10.03.2018</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -12858,25 +13138,25 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Ida Fiskaa Barstad</t>
+          <t>Ina Birgitte Eidsmo Hova</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>1.31,87</t>
+          <t>1.31,48</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>25.10.2020</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -12893,20 +13173,20 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Selma Strandjord Lillerødvann</t>
+          <t>Helle Lundgren</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>1.32,27</t>
+          <t>1.29,34</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>28.01.2024</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -12928,25 +13208,25 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Magne Petersen</t>
+          <t>Ida Fiskaa Barstad</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>1.20,63</t>
+          <t>1.31,87</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>02.03.2013</t>
+          <t>25.10.2020</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -12963,20 +13243,20 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Alice Sophie Mittet</t>
+          <t>Selma Strandjord Lillerødvann</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>1.32,40</t>
+          <t>1.32,27</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>05.03.2016</t>
+          <t>28.01.2024</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -12998,20 +13278,20 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Helle Lundgren</t>
+          <t>Alice Sophie Mittet</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>1.32,62</t>
+          <t>1.32,40</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>17.06.2023</t>
+          <t>05.03.2016</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -13033,25 +13313,25 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Chloe Branlat</t>
+          <t>Magne Petersen</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>1.32,54</t>
+          <t>1.20,63</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>16.02.2025</t>
+          <t>02.03.2013</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -13068,25 +13348,25 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Elsa Dragsten Wake</t>
+          <t>Chloe Branlat</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>1.32,65</t>
+          <t>1.32,54</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>26.04.2025</t>
+          <t>16.02.2025</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kolvereid</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -13103,12 +13383,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Dorthe Marie Schevik</t>
+          <t>Arne Martin Einarsrud Rismoen</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>1.32,78</t>
+          <t>1.20,98</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -13116,7 +13396,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>21.05.2005</t>
+          <t>08.06.2024</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -13138,12 +13418,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Arne Martin Einarsrud Rismoen</t>
+          <t>Dorthe Marie Schevik</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>1.20,98</t>
+          <t>1.32,78</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -13151,7 +13431,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>08.06.2024</t>
+          <t>21.05.2005</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13348,12 +13628,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Inga Victoria Kirabo Nygård</t>
+          <t>Elina Arefjord Spangelo</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>1.35,44</t>
+          <t>1.33,10</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -13361,7 +13641,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>19.06.2022</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13383,20 +13663,20 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Susanne Kolloen</t>
+          <t>Inga Victoria Kirabo Nygård</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>1.35,68</t>
+          <t>1.35,44</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>07.03.2020</t>
+          <t>19.06.2022</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13418,20 +13698,20 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Aurora Johanne Mittet</t>
+          <t>Susanne Kolloen</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>1.35,93</t>
+          <t>1.35,68</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>05.03.2016</t>
+          <t>07.03.2020</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13453,20 +13733,20 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Elina Arefjord Spangelo</t>
+          <t>Aurora Johanne Mittet</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>1.36,09</t>
+          <t>1.35,93</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>26.04.2025</t>
+          <t>05.03.2016</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13698,12 +13978,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Amalie Gylseth Dahl</t>
+          <t>Hedda Gätzschmann</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>1.40,60</t>
+          <t>1.38,15</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -13711,7 +13991,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>01.10.2022</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -13733,25 +14013,25 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Ingrid Skye Naustvoll</t>
+          <t>Amalie Gylseth Dahl</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>1.41,13</t>
+          <t>1.40,60</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>09.11.2013</t>
+          <t>01.10.2022</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -13768,25 +14048,25 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Ingrid Lianes</t>
+          <t>Ingrid Skye Naustvoll</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>1.41,31</t>
+          <t>1.41,13</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>19.04.2009</t>
+          <t>09.11.2013</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -13803,25 +14083,25 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Aurora Dahl Bere</t>
+          <t>Ingrid Lianes</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>1.42,72</t>
+          <t>1.41,31</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>19.04.2009</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -13838,20 +14118,20 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Ronja Emilia Wikström</t>
+          <t>Aurora Dahl Bere</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>1.43,60</t>
+          <t>1.42,72</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>17.06.2023</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -13873,25 +14153,25 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Tora Tveiten</t>
+          <t>Ronja Emilia Wikström</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>1.44,25</t>
+          <t>1.43,60</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>25.10.2014</t>
+          <t>17.06.2023</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -13908,25 +14188,25 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Sigrid Gylseth Dahl</t>
+          <t>Tora Tveiten</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>1.44,37</t>
+          <t>1.44,25</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>25.10.2014</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -13943,25 +14223,25 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Hedda Gätzschmann</t>
+          <t>Sigrid Gylseth Dahl</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>1.45,12</t>
+          <t>1.44,37</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>16.03.2025</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -13978,25 +14258,25 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Else Malin Meidal</t>
+          <t>Marie Wærnes Blom</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>1.45,94</t>
+          <t>1.43,07</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>27.10.2012</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -14013,7 +14293,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Camila Dorao</t>
+          <t>Else Malin Meidal</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14026,12 +14306,12 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>30.09.2023</t>
+          <t>27.10.2012</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -14048,20 +14328,20 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Lea almaas</t>
+          <t>Camila Dorao</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>1.47,10</t>
+          <t>1.45,94</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>03.03.2012</t>
+          <t>30.09.2023</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -14083,20 +14363,20 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Louise Thys</t>
+          <t>Lea almaas</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>1.47,86</t>
+          <t>1.47,10</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>03.03.2012</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -14118,25 +14398,25 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Lena Sofie Hammer</t>
+          <t>Nicoline Vinje</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>1.48,54</t>
+          <t>1.44,91</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>21.05.2005</t>
+          <t>18.10.2025</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -14153,25 +14433,25 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Karoline Skjevik</t>
+          <t>Louise Thys</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>1.48,83</t>
+          <t>1.47,86</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>23.02.2008</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -14188,25 +14468,25 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Nicoline Vinje</t>
+          <t>Live Hamnes Ulriksen</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>1.51,56</t>
+          <t>1.45,61</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>16.03.2025</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -14223,20 +14503,20 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Nora Grande Bjerkan</t>
+          <t>Lena Sofie Hammer</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>1.52,27</t>
+          <t>1.48,54</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>19.06.2010</t>
+          <t>21.05.2005</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -14258,20 +14538,20 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Emilie Caitlin Daquilante</t>
+          <t>Karoline Skjevik</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>1.53,38</t>
+          <t>1.48,83</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>27.10.2012</t>
+          <t>23.02.2008</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -14293,25 +14573,25 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Kaia Winnberg</t>
+          <t>Oda Brennhaug Tangen</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>1.53,99</t>
+          <t>1.48,76</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>17.03.2024</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -14328,20 +14608,20 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Anna Fenstad Høysæter</t>
+          <t>Nora Grande Bjerkan</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>1.54,17</t>
+          <t>1.52,27</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>07.03.2020</t>
+          <t>19.06.2010</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -14363,25 +14643,25 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Ramona Vutudal</t>
+          <t>Emilie Caitlin Daquilante</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>1.55,13</t>
+          <t>1.53,38</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>21.09.2008</t>
+          <t>27.10.2012</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -14398,25 +14678,25 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Amelia Roaldseth</t>
+          <t>Kaia Winnberg</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>1.55,16</t>
+          <t>1.53,99</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>21.09.2008</t>
+          <t>17.03.2024</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -14433,20 +14713,20 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Ilaria Kari Cherubini</t>
+          <t>Anna Fenstad Høysæter</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>1.56,33</t>
+          <t>1.54,17</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>26.04.2025</t>
+          <t>07.03.2020</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -14468,25 +14748,25 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Sara Olea  Riseth Moe</t>
+          <t>Ramona Vutudal</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>1.56,84</t>
+          <t>1.55,13</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>22.02.2025</t>
+          <t>21.09.2008</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -14503,20 +14783,20 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Live Hamnes Ulriksen</t>
+          <t>Amelia Roaldseth</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>1.56,70</t>
+          <t>1.55,16</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>08.12.2024</t>
+          <t>21.09.2008</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -14538,20 +14818,20 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Jassmitha Ajeethsing</t>
+          <t>Sara Olea  Riseth Moe</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>1.57,13</t>
+          <t>1.52,74</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>02.10.2021</t>
+          <t>27.09.2025</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -14573,25 +14853,25 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Marie Wærnes Blom</t>
+          <t>Ilaria Kari Cherubini</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>1.57,55</t>
+          <t>1.56,33</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>06.04.2024</t>
+          <t>26.04.2025</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -14608,25 +14888,25 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Marita Fuglestad Løkken</t>
+          <t>Jassmitha Ajeethsing</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>1.57,94</t>
+          <t>1.57,13</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>09.11.2013</t>
+          <t>02.10.2021</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Hommelvik</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -14643,20 +14923,20 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Phoebe Thalberg Fagerheim</t>
+          <t>Charlotte Talseth</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>1.59,31</t>
+          <t>1.54,75</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>02.03.2013</t>
+          <t>13.09.2025</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -14678,25 +14958,25 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Charlotte Talseth</t>
+          <t>Marita Fuglestad Løkken</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>1.59,34</t>
+          <t>1.57,94</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>26.04.2025</t>
+          <t>09.11.2013</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -14713,25 +14993,25 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Miriam Bianchi Dos Santos</t>
+          <t>Vilma Granhus Følstad</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2.00,90</t>
+          <t>1.55,64</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>08.06.2024</t>
+          <t>01.11.2025</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Hommelvik</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -14748,20 +15028,20 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Camilla Gervasoni</t>
+          <t>Phoebe Thalberg Fagerheim</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2.01,28</t>
+          <t>1.59,31</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>03.03.2012</t>
+          <t>02.03.2013</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -14783,20 +15063,20 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Eline Nergård Wilhelmsen</t>
+          <t>Miriam Bianchi Dos Santos</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2.01,89</t>
+          <t>2.00,90</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>08.12.2024</t>
+          <t>08.06.2024</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -14818,16 +15098,16 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Kristina Bragadottir</t>
+          <t>Camilla Gervasoni</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2.05,14</t>
+          <t>2.01,28</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14853,20 +15133,20 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Hedda Larsen Natvig</t>
+          <t>Eline Nergård Wilhelmsen</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2.05,45</t>
+          <t>2.01,89</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>17.06.2023</t>
+          <t>08.12.2024</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -14888,20 +15168,20 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Regine Nysæther</t>
+          <t>Kristina Bragadottir</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2.05,58</t>
+          <t>2.05,14</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>31.10.2009</t>
+          <t>03.03.2012</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -14923,20 +15203,20 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Connie Rakel Lånke</t>
+          <t>Hedda Larsen Natvig</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2.07,34</t>
+          <t>2.05,45</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>01.03.2014</t>
+          <t>17.06.2023</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -14958,20 +15238,20 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Sofie Havig</t>
+          <t>Regine Nysæther</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2.07,07</t>
+          <t>2.05,58</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>19.03.2006</t>
+          <t>31.10.2009</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -14993,20 +15273,20 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Vilma Granhus Følstad</t>
+          <t>Connie Rakel Lånke</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2.09,07</t>
+          <t>2.07,34</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>01.03.2014</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -15028,20 +15308,20 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Ola Husan</t>
+          <t>Sofie Havig</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>1.55,97</t>
+          <t>2.07,07</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>06.03.2022</t>
+          <t>19.03.2006</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -15063,20 +15343,20 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Snorre Risholt Moen</t>
+          <t>Ola Husan</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2.14,34</t>
+          <t>1.55,97</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>02.03.2013</t>
+          <t>06.03.2022</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -15098,33 +15378,103 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
+          <t>Kristina Kulagina</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2.13,54</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>70</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>01.11.2025</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Hommelvik</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Snorre Risholt Moen</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2.14,34</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>49</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>02.03.2013</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
           <t>KARIANNE HUSBY</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
+      <c r="B201" t="inlineStr">
         <is>
           <t>2.37,37</t>
         </is>
       </c>
-      <c r="C199" t="n">
+      <c r="C201" t="n">
         <v>46</v>
       </c>
-      <c r="D199" t="inlineStr">
+      <c r="D201" t="inlineStr">
         <is>
           <t>13.03.2010</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>Trondheim</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>25m</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
